--- a/data/trans_orig/P25D_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P25D_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la forma de consumir tabaco no tradicional  (se incluyen pipas de agua, cachimbas, vapeadores, cigarrillos electrónicos) en 2023</t>
+          <t>Población según la forma de consumir tabaco no tradicional  (se incluyen pipas de agua, cachimbas, vapeadores, cigarrillos electrónicos) en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>4392</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22965</t>
+          <t>23811</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>8918</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24939</t>
+          <t>25317</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15716</t>
+          <t>15825</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38671</t>
+          <t>39323</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2394</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12428</t>
+          <t>11444</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34413</t>
+          <t>34783</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>9675</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39642</t>
+          <t>40077</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>811</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7198</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>830</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7728</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>10727</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11783</t>
+          <t>10710</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14197</t>
+          <t>14456</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15632</t>
+          <t>16000</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>472684</t>
+          <t>473149</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>497251</t>
+          <t>496718</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>705220</t>
+          <t>705559</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>735544</t>
+          <t>735571</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1189733</t>
+          <t>1190418</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1226961</t>
+          <t>1226956</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55885</t>
+          <t>55066</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>112732</t>
+          <t>110274</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55548</t>
+          <t>53680</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>98331</t>
+          <t>98972</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,47 +1575,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>161771</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>126246</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>198789</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>4,4%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>161771</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>128258</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>197915</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20835</t>
+          <t>20644</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50671</t>
+          <t>53054</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>17020</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36882</t>
+          <t>36890</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42234</t>
+          <t>42991</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>80488</t>
+          <t>79214</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12146</t>
+          <t>12939</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40774</t>
+          <t>42598</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9142</t>
+          <t>9100</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29660</t>
+          <t>29222</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,42 +1806,42 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>40243</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>26041</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>60076</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>1,33%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>40243</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>26406</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>59508</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17155</t>
+          <t>17660</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53597</t>
+          <t>54369</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10608</t>
+          <t>11338</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33646</t>
+          <t>33842</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34766</t>
+          <t>35300</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75934</t>
+          <t>75800</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23495</t>
+          <t>20863</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>956587</t>
+          <t>776427</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3699</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20389</t>
+          <t>19659</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>27412</t>
+          <t>27858</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1113446</t>
+          <t>1034639</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>22,91%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1232996</t>
+          <t>1374067</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2072561</t>
+          <t>2073233</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2055182</t>
+          <t>2053260</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2127381</t>
+          <t>2129504</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,17 +2155,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3925039</t>
+          <t>3925040</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3153831</t>
+          <t>3226506</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4171386</t>
+          <t>4167894</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,28%</t>
         </is>
       </c>
     </row>
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4516722</t>
+          <t>4516723</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4516722</t>
+          <t>4516723</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4516722</t>
+          <t>4516723</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10216</t>
+          <t>10555</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26210</t>
+          <t>26304</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13894</t>
+          <t>14039</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31518</t>
+          <t>30736</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>27941</t>
+          <t>28224</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>49539</t>
+          <t>50396</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5570</t>
+          <t>5770</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20805</t>
+          <t>20918</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6552</t>
+          <t>6468</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8683</t>
+          <t>8724</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23505</t>
+          <t>25603</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22237</t>
+          <t>20209</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>3767</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13159</t>
+          <t>12914</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11163</t>
+          <t>11095</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>28039</t>
+          <t>29505</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14961</t>
+          <t>13635</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>426</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>5255</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15412</t>
+          <t>13573</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15154</t>
+          <t>15715</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15083</t>
+          <t>16281</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22755</t>
+          <t>22285</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>581004</t>
+          <t>580173</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>611484</t>
+          <t>611448</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>606554</t>
+          <t>607497</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>630083</t>
+          <t>630440</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1200748</t>
+          <t>1200643</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1236869</t>
+          <t>1236715</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,81%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>81713</t>
+          <t>81994</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>139484</t>
+          <t>141073</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>88011</t>
+          <t>90328</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>137606</t>
+          <t>135596</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>189015</t>
+          <t>181170</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>261628</t>
+          <t>261618</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>34592</t>
+          <t>34887</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>68870</t>
+          <t>69432</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>28088</t>
+          <t>27964</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>61668</t>
+          <t>62516</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>71845</t>
+          <t>71857</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>117613</t>
+          <t>120847</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>23694</t>
+          <t>23422</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>55899</t>
+          <t>56074</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>15843</t>
+          <t>15293</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>36046</t>
+          <t>35587</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>44544</t>
+          <t>43864</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>83926</t>
+          <t>80124</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22839</t>
+          <t>22590</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>58295</t>
+          <t>59998</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13688</t>
+          <t>14397</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>36341</t>
+          <t>37586</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>43377</t>
+          <t>43126</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>86636</t>
+          <t>85544</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29423</t>
+          <t>29584</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1129972</t>
+          <t>1062961</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8731</t>
+          <t>8357</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29434</t>
+          <t>28176</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>43872</t>
+          <t>43122</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1255698</t>
+          <t>1143112</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2161059</t>
+          <t>2232376</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3166304</t>
+          <t>3164480</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3397357</t>
+          <t>3395239</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3475866</t>
+          <t>3471979</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,47 +3730,47 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
+          <t>93,09%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>95,2%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>8153</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>6358336</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>5558348</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>6603945</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>89,68%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>78,4%</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
           <t>93,15%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>95,3%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>8153</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>6358336</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>5522859</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>6606385</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>89,68%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>77,9%</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>93,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25D_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P25D_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>10815</t>
+          <t>11707</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4392</t>
+          <t>5438</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23811</t>
+          <t>24559</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14164</t>
+          <t>16118</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8918</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25317</t>
+          <t>27414</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>24979</t>
+          <t>27826</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15825</t>
+          <t>16864</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39323</t>
+          <t>41345</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>7920</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>3361</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11444</t>
+          <t>14833</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11781</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34783</t>
+          <t>12679</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>17486</t>
+          <t>14984</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9675</t>
+          <t>8748</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40077</t>
+          <t>23327</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>893</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>8451</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>901</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6824</t>
+          <t>8744</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>5829</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1693</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10727</t>
+          <t>15168</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>723</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3465</t>
+          <t>4541</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4417</t>
+          <t>6552</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10710</t>
+          <t>15009</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14456</t>
+          <t>13557</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>935</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2938</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>6260</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2370</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16000</t>
+          <t>14192</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>486587</t>
+          <t>544903</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>473149</t>
+          <t>529958</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>496718</t>
+          <t>555760</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>726160</t>
+          <t>795116</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>705559</t>
+          <t>784389</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>735571</t>
+          <t>803253</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1212747</t>
+          <t>1340020</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1190418</t>
+          <t>1321994</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1226956</t>
+          <t>1355132</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>753600</t>
+          <t>819957</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>753600</t>
+          <t>819957</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>753600</t>
+          <t>819957</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1268538</t>
+          <t>1398486</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1268538</t>
+          <t>1398486</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1268538</t>
+          <t>1398486</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83428</t>
+          <t>88409</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55066</t>
+          <t>68261</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>110274</t>
+          <t>113130</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>78343</t>
+          <t>87334</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53680</t>
+          <t>71536</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>98972</t>
+          <t>106568</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>161771</t>
+          <t>175743</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>126246</t>
+          <t>148280</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>198789</t>
+          <t>208526</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34207</t>
+          <t>38726</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20644</t>
+          <t>26877</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53054</t>
+          <t>55577</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25947</t>
+          <t>26833</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17020</t>
+          <t>17903</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36890</t>
+          <t>36878</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>60153</t>
+          <t>65559</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42991</t>
+          <t>49434</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>79214</t>
+          <t>83761</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23797</t>
+          <t>28257</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12939</t>
+          <t>17400</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42598</t>
+          <t>45534</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>17690</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9100</t>
+          <t>10357</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29222</t>
+          <t>28887</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>40243</t>
+          <t>45947</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26041</t>
+          <t>31055</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60076</t>
+          <t>66371</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>31106</t>
+          <t>35430</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17660</t>
+          <t>22614</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54369</t>
+          <t>56022</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>20405</t>
+          <t>23580</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11338</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33842</t>
+          <t>40765</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>51511</t>
+          <t>59010</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35300</t>
+          <t>42053</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75800</t>
+          <t>82281</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>269721</t>
+          <t>24125</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20863</t>
+          <t>11553</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>776427</t>
+          <t>45002</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8283</t>
+          <t>12338</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3699</t>
+          <t>6110</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19659</t>
+          <t>25154</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>278005</t>
+          <t>36462</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>27858</t>
+          <t>21128</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1034639</t>
+          <t>59368</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1840728</t>
+          <t>2008031</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1374067</t>
+          <t>1971901</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2073233</t>
+          <t>2042292</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2084311</t>
+          <t>1999225</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2053260</t>
+          <t>1972304</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2129504</t>
+          <t>2022610</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3925040</t>
+          <t>4007256</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3226506</t>
+          <t>3963900</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4167894</t>
+          <t>4057967</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,44%</t>
         </is>
       </c>
     </row>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2282987</t>
+          <t>2222977</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2282987</t>
+          <t>2222977</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2282987</t>
+          <t>2222977</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2233735</t>
+          <t>2167000</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2233735</t>
+          <t>2167000</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2233735</t>
+          <t>2167000</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4516723</t>
+          <t>4389977</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4516723</t>
+          <t>4389977</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4516723</t>
+          <t>4389977</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>16931</t>
+          <t>19148</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10555</t>
+          <t>12592</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26304</t>
+          <t>29803</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>20571</t>
+          <t>22127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14039</t>
+          <t>14747</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30736</t>
+          <t>32287</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,27 +2385,27 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>37502</t>
+          <t>41275</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28224</t>
+          <t>30616</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>50396</t>
+          <t>55762</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10893</t>
+          <t>13076</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20918</t>
+          <t>24385</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6468</t>
+          <t>7866</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>13926</t>
+          <t>16838</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8724</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25603</t>
+          <t>29054</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -2541,22 +2541,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>10964</t>
+          <t>11449</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20209</t>
+          <t>20860</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7294</t>
+          <t>8254</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3767</t>
+          <t>4087</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12914</t>
+          <t>14087</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>18259</t>
+          <t>19703</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11095</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>29505</t>
+          <t>30083</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>3534</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13635</t>
+          <t>16926</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>467</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5255</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,22 +2724,22 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>5515</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13573</t>
+          <t>15559</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2777,12 +2777,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15715</t>
+          <t>20582</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6049</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16281</t>
+          <t>15288</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>9160</t>
+          <t>9352</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22285</t>
+          <t>21005</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>599490</t>
+          <t>659447</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>580173</t>
+          <t>641855</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>611448</t>
+          <t>672782</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>621060</t>
+          <t>691593</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>607497</t>
+          <t>677521</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>630440</t>
+          <t>702076</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,27 +2950,27 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1220549</t>
+          <t>1351041</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1200643</t>
+          <t>1330540</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1236715</t>
+          <t>1368852</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -2993,17 +2993,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>644610</t>
+          <t>709555</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>644610</t>
+          <t>709555</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>644610</t>
+          <t>709555</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>659812</t>
+          <t>734168</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>659812</t>
+          <t>734168</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>659812</t>
+          <t>734168</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1304421</t>
+          <t>1443724</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1304421</t>
+          <t>1443724</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1304421</t>
+          <t>1443724</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>111174</t>
+          <t>119264</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>81994</t>
+          <t>95998</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>141073</t>
+          <t>147951</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>113078</t>
+          <t>125579</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>90328</t>
+          <t>105052</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>135596</t>
+          <t>150388</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>224253</t>
+          <t>244844</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>181170</t>
+          <t>213534</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>261618</t>
+          <t>280076</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -3223,67 +3223,67 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>50804</t>
+          <t>59722</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>34887</t>
+          <t>45144</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>69432</t>
+          <t>79045</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>37660</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>28236</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>40760</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>27964</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>62516</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>91565</t>
+          <t>97381</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>71857</t>
+          <t>78250</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>120847</t>
+          <t>120412</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>37411</t>
+          <t>42606</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>23422</t>
+          <t>28873</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>56074</t>
+          <t>63540</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>23740</t>
+          <t>25944</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>15293</t>
+          <t>17394</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>35587</t>
+          <t>39096</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>61151</t>
+          <t>68550</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>43864</t>
+          <t>51346</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>80124</t>
+          <t>89534</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>38109</t>
+          <t>44793</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22590</t>
+          <t>29777</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>59998</t>
+          <t>66556</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>22845</t>
+          <t>26285</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>14397</t>
+          <t>16812</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>37586</t>
+          <t>40308</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>60953</t>
+          <t>71078</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>43126</t>
+          <t>52448</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>85544</t>
+          <t>100449</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>278232</t>
+          <t>32294</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29584</t>
+          <t>17625</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1062961</t>
+          <t>54193</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>15192</t>
+          <t>19723</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8357</t>
+          <t>11248</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28176</t>
+          <t>34174</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>293424</t>
+          <t>52017</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>43122</t>
+          <t>32472</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1143112</t>
+          <t>75460</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2926805</t>
+          <t>3212381</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2232376</t>
+          <t>3161498</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3164480</t>
+          <t>3247361</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3431531</t>
+          <t>3485935</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3395239</t>
+          <t>3454998</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3471979</t>
+          <t>3515732</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>6358336</t>
+          <t>6698317</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5558348</t>
+          <t>6646515</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6603945</t>
+          <t>6751319</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3442535</t>
+          <t>3511061</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3442535</t>
+          <t>3511061</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3442535</t>
+          <t>3511061</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3647147</t>
+          <t>3721125</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3647147</t>
+          <t>3721125</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3647147</t>
+          <t>3721125</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>7089682</t>
+          <t>7232187</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7089682</t>
+          <t>7232187</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7089682</t>
+          <t>7232187</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
